--- a/public/samples/spws/ptfeenvelope.xlsx
+++ b/public/samples/spws/ptfeenvelope.xlsx
@@ -1,31 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/leanhtu/Desktop/merge/project_freelance/KHO/kho SPW/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50066460-02FD-614B-941F-84E434210100}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="960" windowWidth="27640" windowHeight="15440" xr2:uid="{B785AC85-88C9-3E42-A56D-CB6164786A23}"/>
+    <workbookView windowWidth="28800" windowHeight="12040"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="48">
   <si>
     <t>Tồn</t>
   </si>
@@ -62,6 +51,9 @@
   </si>
   <si>
     <t>Date</t>
+  </si>
+  <si>
+    <t>Đơn giá</t>
   </si>
   <si>
     <t>ENPT V 030 J05 0015</t>
@@ -172,29 +164,370 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="d&quot;/&quot;m&quot;/&quot;yyyy"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="6">
+    <numFmt numFmtId="176" formatCode="d&quot;/&quot;m&quot;/&quot;yyyy"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="42" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="21">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -202,26 +535,312 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="60% - Accent6" xfId="1" builtinId="52"/>
+    <cellStyle name="40% - Accent6" xfId="2" builtinId="51"/>
+    <cellStyle name="60% - Accent5" xfId="3" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="4" builtinId="49"/>
+    <cellStyle name="40% - Accent5" xfId="5" builtinId="47"/>
+    <cellStyle name="20% - Accent5" xfId="6" builtinId="46"/>
+    <cellStyle name="60% - Accent4" xfId="7" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="8" builtinId="45"/>
+    <cellStyle name="40% - Accent4" xfId="9" builtinId="43"/>
+    <cellStyle name="Accent4" xfId="10" builtinId="41"/>
+    <cellStyle name="Linked Cell" xfId="11" builtinId="24"/>
+    <cellStyle name="40% - Accent3" xfId="12" builtinId="39"/>
+    <cellStyle name="60% - Accent2" xfId="13" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="14" builtinId="37"/>
+    <cellStyle name="40% - Accent2" xfId="15" builtinId="35"/>
+    <cellStyle name="20% - Accent2" xfId="16" builtinId="34"/>
+    <cellStyle name="Accent2" xfId="17" builtinId="33"/>
+    <cellStyle name="40% - Accent1" xfId="18" builtinId="31"/>
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30"/>
+    <cellStyle name="Accent1" xfId="20" builtinId="29"/>
+    <cellStyle name="Neutral" xfId="21" builtinId="28"/>
+    <cellStyle name="60% - Accent1" xfId="22" builtinId="32"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="20% - Accent4" xfId="24" builtinId="42"/>
+    <cellStyle name="Total" xfId="25" builtinId="25"/>
+    <cellStyle name="Output" xfId="26" builtinId="21"/>
+    <cellStyle name="Currency" xfId="27" builtinId="4"/>
+    <cellStyle name="20% - Accent3" xfId="28" builtinId="38"/>
+    <cellStyle name="Note" xfId="29" builtinId="10"/>
+    <cellStyle name="Input" xfId="30" builtinId="20"/>
+    <cellStyle name="Heading 4" xfId="31" builtinId="19"/>
+    <cellStyle name="Calculation" xfId="32" builtinId="22"/>
+    <cellStyle name="Good" xfId="33" builtinId="26"/>
+    <cellStyle name="Heading 3" xfId="34" builtinId="18"/>
+    <cellStyle name="CExplanatory Text" xfId="35" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="36" builtinId="16"/>
+    <cellStyle name="Comma [0]" xfId="37" builtinId="6"/>
+    <cellStyle name="20% - Accent6" xfId="38" builtinId="50"/>
+    <cellStyle name="Title" xfId="39" builtinId="15"/>
+    <cellStyle name="Currency [0]" xfId="40" builtinId="7"/>
+    <cellStyle name="Warning Text" xfId="41" builtinId="11"/>
+    <cellStyle name="Followed Hyperlink" xfId="42" builtinId="9"/>
+    <cellStyle name="Heading 2" xfId="43" builtinId="17"/>
+    <cellStyle name="Comma" xfId="44" builtinId="3"/>
+    <cellStyle name="Check Cell" xfId="45" builtinId="23"/>
+    <cellStyle name="60% - Accent3" xfId="46" builtinId="40"/>
+    <cellStyle name="Percent" xfId="47" builtinId="5"/>
+    <cellStyle name="Hyperlink" xfId="48" builtinId="8"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -270,7 +889,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -303,26 +922,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -355,23 +957,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -513,27 +1098,22 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{503DF095-8A60-CA44-AEB6-6644FCA49A97}">
-  <dimension ref="A1:L44"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:M44"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.8"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="K1" s="1"/>
+    <row r="1" spans="11:12">
+      <c r="K1" s="2"/>
       <c r="L1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -564,28 +1144,31 @@
       <c r="J2" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="2" t="s">
         <v>11</v>
       </c>
       <c r="L2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="2">
+        <v>14</v>
+      </c>
+      <c r="C3" s="1">
         <v>3</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F3">
         <v>54</v>
@@ -597,31 +1180,31 @@
         <v>97</v>
       </c>
       <c r="I3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K3" s="1"/>
+        <v>18</v>
+      </c>
+      <c r="K3" s="2"/>
       <c r="L3">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="2">
+        <v>14</v>
+      </c>
+      <c r="C4" s="1">
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F4">
         <v>59</v>
@@ -633,31 +1216,31 @@
         <v>89</v>
       </c>
       <c r="I4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J4" t="s">
-        <v>17</v>
-      </c>
-      <c r="K4" s="1"/>
+        <v>18</v>
+      </c>
+      <c r="K4" s="2"/>
       <c r="L4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="2">
+        <v>14</v>
+      </c>
+      <c r="C5" s="1">
         <v>3</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F5">
         <v>70</v>
@@ -669,31 +1252,31 @@
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J5" t="s">
-        <v>17</v>
-      </c>
-      <c r="K5" s="1"/>
+        <v>18</v>
+      </c>
+      <c r="K5" s="2"/>
       <c r="L5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="2">
+        <v>14</v>
+      </c>
+      <c r="C6" s="1">
         <v>3</v>
       </c>
       <c r="D6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F6">
         <v>79</v>
@@ -705,31 +1288,31 @@
         <v>240</v>
       </c>
       <c r="I6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J6" t="s">
-        <v>17</v>
-      </c>
-      <c r="K6" s="1"/>
+        <v>18</v>
+      </c>
+      <c r="K6" s="2"/>
       <c r="L6">
         <v>95</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="2">
+        <v>14</v>
+      </c>
+      <c r="C7" s="1">
         <v>3</v>
       </c>
       <c r="D7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F7">
         <v>85</v>
@@ -741,31 +1324,31 @@
         <v>46</v>
       </c>
       <c r="I7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J7" t="s">
-        <v>17</v>
-      </c>
-      <c r="K7" s="1"/>
+        <v>18</v>
+      </c>
+      <c r="K7" s="2"/>
       <c r="L7">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="2">
+        <v>14</v>
+      </c>
+      <c r="C8" s="1">
         <v>3</v>
       </c>
       <c r="D8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F8">
         <v>99</v>
@@ -777,31 +1360,31 @@
         <v>154</v>
       </c>
       <c r="I8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J8" t="s">
-        <v>17</v>
-      </c>
-      <c r="K8" s="1"/>
+        <v>18</v>
+      </c>
+      <c r="K8" s="2"/>
       <c r="L8">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="2">
+        <v>14</v>
+      </c>
+      <c r="C9" s="1">
         <v>3</v>
       </c>
       <c r="D9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F9">
         <v>119</v>
@@ -813,31 +1396,31 @@
         <v>183</v>
       </c>
       <c r="I9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J9" t="s">
-        <v>17</v>
-      </c>
-      <c r="K9" s="1"/>
+        <v>18</v>
+      </c>
+      <c r="K9" s="2"/>
       <c r="L9">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="2">
+        <v>14</v>
+      </c>
+      <c r="C10" s="1">
         <v>3</v>
       </c>
       <c r="D10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F10">
         <v>129</v>
@@ -849,31 +1432,31 @@
         <v>270</v>
       </c>
       <c r="I10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J10" t="s">
-        <v>17</v>
-      </c>
-      <c r="K10" s="1"/>
+        <v>18</v>
+      </c>
+      <c r="K10" s="2"/>
       <c r="L10">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" s="2">
+        <v>14</v>
+      </c>
+      <c r="C11" s="1">
         <v>3</v>
       </c>
       <c r="D11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F11">
         <v>140</v>
@@ -885,31 +1468,31 @@
         <v>238</v>
       </c>
       <c r="I11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J11" t="s">
-        <v>17</v>
-      </c>
-      <c r="K11" s="1"/>
+        <v>18</v>
+      </c>
+      <c r="K11" s="2"/>
       <c r="L11">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12">
       <c r="A12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" s="2">
+        <v>14</v>
+      </c>
+      <c r="C12" s="1">
         <v>3</v>
       </c>
       <c r="D12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F12">
         <v>155</v>
@@ -921,31 +1504,31 @@
         <v>292</v>
       </c>
       <c r="I12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J12" t="s">
-        <v>17</v>
-      </c>
-      <c r="K12" s="1"/>
+        <v>18</v>
+      </c>
+      <c r="K12" s="2"/>
       <c r="L12">
         <v>264</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" s="2">
+        <v>14</v>
+      </c>
+      <c r="C13" s="1">
         <v>3</v>
       </c>
       <c r="D13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F13">
         <v>185</v>
@@ -957,31 +1540,31 @@
         <v>220</v>
       </c>
       <c r="I13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J13" t="s">
-        <v>17</v>
-      </c>
-      <c r="K13" s="1"/>
+        <v>18</v>
+      </c>
+      <c r="K13" s="2"/>
       <c r="L13">
         <v>55</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>13</v>
-      </c>
-      <c r="C14" s="2">
+        <v>14</v>
+      </c>
+      <c r="C14" s="1">
         <v>3</v>
       </c>
       <c r="D14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F14">
         <v>215</v>
@@ -993,31 +1576,31 @@
         <v>134</v>
       </c>
       <c r="I14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J14" t="s">
-        <v>17</v>
-      </c>
-      <c r="K14" s="1"/>
+        <v>18</v>
+      </c>
+      <c r="K14" s="2"/>
       <c r="L14">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12">
       <c r="A15" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B15" t="s">
-        <v>13</v>
-      </c>
-      <c r="C15" s="2">
+        <v>14</v>
+      </c>
+      <c r="C15" s="1">
         <v>3</v>
       </c>
       <c r="D15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F15">
         <v>240</v>
@@ -1029,31 +1612,31 @@
         <v>95</v>
       </c>
       <c r="I15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J15" t="s">
-        <v>17</v>
-      </c>
-      <c r="K15" s="1"/>
+        <v>18</v>
+      </c>
+      <c r="K15" s="2"/>
       <c r="L15">
         <v>92</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C16" s="2">
+        <v>14</v>
+      </c>
+      <c r="C16" s="1">
         <v>3</v>
       </c>
       <c r="D16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F16">
         <v>54</v>
@@ -1065,33 +1648,33 @@
         <v>200</v>
       </c>
       <c r="I16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J16" t="s">
-        <v>17</v>
-      </c>
-      <c r="K16" s="1">
+        <v>18</v>
+      </c>
+      <c r="K16" s="2">
         <v>44414</v>
       </c>
       <c r="L16">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B17" t="s">
-        <v>13</v>
-      </c>
-      <c r="C17" s="2">
+        <v>14</v>
+      </c>
+      <c r="C17" s="1">
         <v>3</v>
       </c>
       <c r="D17" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F17">
         <v>59</v>
@@ -1103,33 +1686,33 @@
         <v>200</v>
       </c>
       <c r="I17" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J17" t="s">
-        <v>17</v>
-      </c>
-      <c r="K17" s="1">
+        <v>18</v>
+      </c>
+      <c r="K17" s="2">
         <v>44414</v>
       </c>
       <c r="L17">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12">
       <c r="A18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B18" t="s">
-        <v>13</v>
-      </c>
-      <c r="C18" s="2">
+        <v>14</v>
+      </c>
+      <c r="C18" s="1">
         <v>3</v>
       </c>
       <c r="D18" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E18" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F18">
         <v>70</v>
@@ -1141,33 +1724,33 @@
         <v>300</v>
       </c>
       <c r="I18" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J18" t="s">
-        <v>17</v>
-      </c>
-      <c r="K18" s="1">
+        <v>18</v>
+      </c>
+      <c r="K18" s="2">
         <v>44414</v>
       </c>
       <c r="L18">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B19" t="s">
-        <v>13</v>
-      </c>
-      <c r="C19" s="2">
+        <v>14</v>
+      </c>
+      <c r="C19" s="1">
         <v>3</v>
       </c>
       <c r="D19" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E19" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F19">
         <v>79</v>
@@ -1179,33 +1762,33 @@
         <v>100</v>
       </c>
       <c r="I19" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J19" t="s">
-        <v>17</v>
-      </c>
-      <c r="K19" s="1">
+        <v>18</v>
+      </c>
+      <c r="K19" s="2">
         <v>44414</v>
       </c>
       <c r="L19">
         <v>100</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12">
       <c r="A20" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>13</v>
-      </c>
-      <c r="C20" s="2">
+        <v>14</v>
+      </c>
+      <c r="C20" s="1">
         <v>3</v>
       </c>
       <c r="D20" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E20" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F20">
         <v>85</v>
@@ -1217,33 +1800,33 @@
         <v>200</v>
       </c>
       <c r="I20" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J20" t="s">
-        <v>17</v>
-      </c>
-      <c r="K20" s="1">
+        <v>18</v>
+      </c>
+      <c r="K20" s="2">
         <v>44414</v>
       </c>
       <c r="L20">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12">
       <c r="A21" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B21" t="s">
-        <v>13</v>
-      </c>
-      <c r="C21" s="2">
+        <v>14</v>
+      </c>
+      <c r="C21" s="1">
         <v>3</v>
       </c>
       <c r="D21" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E21" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F21">
         <v>99</v>
@@ -1255,33 +1838,33 @@
         <v>200</v>
       </c>
       <c r="I21" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J21" t="s">
-        <v>17</v>
-      </c>
-      <c r="K21" s="1">
+        <v>18</v>
+      </c>
+      <c r="K21" s="2">
         <v>44414</v>
       </c>
       <c r="L21">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12">
       <c r="A22" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>13</v>
-      </c>
-      <c r="C22" s="2">
+        <v>14</v>
+      </c>
+      <c r="C22" s="1">
         <v>3</v>
       </c>
       <c r="D22" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E22" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F22">
         <v>119</v>
@@ -1293,33 +1876,33 @@
         <v>100</v>
       </c>
       <c r="I22" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J22" t="s">
-        <v>17</v>
-      </c>
-      <c r="K22" s="1">
+        <v>18</v>
+      </c>
+      <c r="K22" s="2">
         <v>44414</v>
       </c>
       <c r="L22">
         <v>33</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12">
       <c r="A23" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B23" t="s">
-        <v>13</v>
-      </c>
-      <c r="C23" s="2">
+        <v>14</v>
+      </c>
+      <c r="C23" s="1">
         <v>3</v>
       </c>
       <c r="D23" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E23" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F23">
         <v>129</v>
@@ -1331,33 +1914,33 @@
         <v>100</v>
       </c>
       <c r="I23" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J23" t="s">
-        <v>17</v>
-      </c>
-      <c r="K23" s="1">
+        <v>18</v>
+      </c>
+      <c r="K23" s="2">
         <v>44414</v>
       </c>
       <c r="L23">
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12">
       <c r="A24" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B24" t="s">
-        <v>13</v>
-      </c>
-      <c r="C24" s="2">
+        <v>14</v>
+      </c>
+      <c r="C24" s="1">
         <v>3</v>
       </c>
       <c r="D24" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E24" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F24">
         <v>140</v>
@@ -1369,33 +1952,33 @@
         <v>100</v>
       </c>
       <c r="I24" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J24" t="s">
-        <v>17</v>
-      </c>
-      <c r="K24" s="1">
+        <v>18</v>
+      </c>
+      <c r="K24" s="2">
         <v>44414</v>
       </c>
       <c r="L24">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12">
       <c r="A25" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B25" t="s">
-        <v>13</v>
-      </c>
-      <c r="C25" s="2">
+        <v>14</v>
+      </c>
+      <c r="C25" s="1">
         <v>3</v>
       </c>
       <c r="D25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E25" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F25">
         <v>155</v>
@@ -1407,33 +1990,33 @@
         <v>100</v>
       </c>
       <c r="I25" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J25" t="s">
-        <v>17</v>
-      </c>
-      <c r="K25" s="1">
+        <v>18</v>
+      </c>
+      <c r="K25" s="2">
         <v>44414</v>
       </c>
       <c r="L25">
         <v>100</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12">
       <c r="A26" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B26" t="s">
-        <v>13</v>
-      </c>
-      <c r="C26" s="2">
+        <v>14</v>
+      </c>
+      <c r="C26" s="1">
         <v>3</v>
       </c>
       <c r="D26" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E26" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F26">
         <v>185</v>
@@ -1445,33 +2028,33 @@
         <v>100</v>
       </c>
       <c r="I26" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J26" t="s">
-        <v>17</v>
-      </c>
-      <c r="K26" s="1">
+        <v>18</v>
+      </c>
+      <c r="K26" s="2">
         <v>44414</v>
       </c>
       <c r="L26">
         <v>65</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12">
       <c r="A27" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>13</v>
-      </c>
-      <c r="C27" s="2">
+        <v>14</v>
+      </c>
+      <c r="C27" s="1">
         <v>3</v>
       </c>
       <c r="D27" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E27" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F27">
         <v>215</v>
@@ -1483,33 +2066,33 @@
         <v>100</v>
       </c>
       <c r="I27" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J27" t="s">
-        <v>17</v>
-      </c>
-      <c r="K27" s="1">
+        <v>18</v>
+      </c>
+      <c r="K27" s="2">
         <v>44414</v>
       </c>
       <c r="L27">
         <v>54</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12">
       <c r="A28" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B28" t="s">
-        <v>13</v>
-      </c>
-      <c r="C28" s="2">
+        <v>14</v>
+      </c>
+      <c r="C28" s="1">
         <v>3</v>
       </c>
       <c r="D28" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E28" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F28">
         <v>240</v>
@@ -1521,33 +2104,33 @@
         <v>100</v>
       </c>
       <c r="I28" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J28" t="s">
-        <v>17</v>
-      </c>
-      <c r="K28" s="1">
+        <v>18</v>
+      </c>
+      <c r="K28" s="2">
         <v>44414</v>
       </c>
       <c r="L28">
         <v>100</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:12">
       <c r="A29" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B29" t="s">
-        <v>13</v>
-      </c>
-      <c r="C29" s="2">
+        <v>14</v>
+      </c>
+      <c r="C29" s="1">
         <v>3</v>
       </c>
       <c r="D29" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E29" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F29">
         <v>59</v>
@@ -1559,33 +2142,33 @@
         <v>200</v>
       </c>
       <c r="I29" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J29" t="s">
-        <v>17</v>
-      </c>
-      <c r="K29" s="1">
+        <v>18</v>
+      </c>
+      <c r="K29" s="2">
         <v>44503</v>
       </c>
       <c r="L29">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:12">
       <c r="A30" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B30" t="s">
-        <v>13</v>
-      </c>
-      <c r="C30" s="2">
+        <v>14</v>
+      </c>
+      <c r="C30" s="1">
         <v>3</v>
       </c>
       <c r="D30" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E30" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F30">
         <v>70</v>
@@ -1597,33 +2180,33 @@
         <v>300</v>
       </c>
       <c r="I30" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J30" t="s">
-        <v>17</v>
-      </c>
-      <c r="K30" s="1">
+        <v>18</v>
+      </c>
+      <c r="K30" s="2">
         <v>44503</v>
       </c>
       <c r="L30">
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B31" t="s">
-        <v>13</v>
-      </c>
-      <c r="C31" s="2">
+        <v>14</v>
+      </c>
+      <c r="C31" s="1">
         <v>3</v>
       </c>
       <c r="D31" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E31" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F31">
         <v>85</v>
@@ -1635,33 +2218,33 @@
         <v>400</v>
       </c>
       <c r="I31" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J31" t="s">
-        <v>17</v>
-      </c>
-      <c r="K31" s="1">
+        <v>18</v>
+      </c>
+      <c r="K31" s="2">
         <v>44503</v>
       </c>
       <c r="L31">
         <v>135</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12">
       <c r="A32" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B32" t="s">
-        <v>13</v>
-      </c>
-      <c r="C32" s="2">
+        <v>14</v>
+      </c>
+      <c r="C32" s="1">
         <v>3</v>
       </c>
       <c r="D32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E32" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F32">
         <v>99</v>
@@ -1673,33 +2256,33 @@
         <v>100</v>
       </c>
       <c r="I32" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J32" t="s">
-        <v>17</v>
-      </c>
-      <c r="K32" s="1">
+        <v>18</v>
+      </c>
+      <c r="K32" s="2">
         <v>44503</v>
       </c>
       <c r="L32">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:12">
       <c r="A33" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B33" t="s">
-        <v>13</v>
-      </c>
-      <c r="C33" s="2">
+        <v>14</v>
+      </c>
+      <c r="C33" s="1">
         <v>3</v>
       </c>
       <c r="D33" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E33" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F33">
         <v>119</v>
@@ -1711,33 +2294,33 @@
         <v>100</v>
       </c>
       <c r="I33" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J33" t="s">
-        <v>17</v>
-      </c>
-      <c r="K33" s="1">
+        <v>18</v>
+      </c>
+      <c r="K33" s="2">
         <v>44503</v>
       </c>
       <c r="L33">
         <v>100</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:12">
       <c r="A34" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>13</v>
-      </c>
-      <c r="C34" s="2">
+        <v>14</v>
+      </c>
+      <c r="C34" s="1">
         <v>3</v>
       </c>
       <c r="D34" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E34" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F34">
         <v>129</v>
@@ -1749,33 +2332,33 @@
         <v>200</v>
       </c>
       <c r="I34" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J34" t="s">
-        <v>17</v>
-      </c>
-      <c r="K34" s="1">
+        <v>18</v>
+      </c>
+      <c r="K34" s="2">
         <v>44503</v>
       </c>
       <c r="L34">
         <v>82</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:12">
       <c r="A35" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>13</v>
-      </c>
-      <c r="C35" s="2">
+        <v>14</v>
+      </c>
+      <c r="C35" s="1">
         <v>3</v>
       </c>
       <c r="D35" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E35" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F35">
         <v>155</v>
@@ -1787,33 +2370,33 @@
         <v>300</v>
       </c>
       <c r="I35" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J35" t="s">
-        <v>17</v>
-      </c>
-      <c r="K35" s="1">
+        <v>18</v>
+      </c>
+      <c r="K35" s="2">
         <v>44503</v>
       </c>
       <c r="L35">
         <v>276</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:12">
       <c r="A36" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>13</v>
-      </c>
-      <c r="C36" s="2">
+        <v>14</v>
+      </c>
+      <c r="C36" s="1">
         <v>3</v>
       </c>
       <c r="D36" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E36" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F36">
         <v>215</v>
@@ -1825,33 +2408,33 @@
         <v>200</v>
       </c>
       <c r="I36" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J36" t="s">
-        <v>17</v>
-      </c>
-      <c r="K36" s="1">
+        <v>18</v>
+      </c>
+      <c r="K36" s="2">
         <v>44503</v>
       </c>
       <c r="L36">
         <v>200</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:12">
       <c r="A37" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B37" t="s">
-        <v>13</v>
-      </c>
-      <c r="C37" s="2">
+        <v>14</v>
+      </c>
+      <c r="C37" s="1">
         <v>3</v>
       </c>
       <c r="D37" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E37" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F37">
         <v>265</v>
@@ -1863,33 +2446,33 @@
         <v>200</v>
       </c>
       <c r="I37" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J37" t="s">
-        <v>17</v>
-      </c>
-      <c r="K37" s="1">
+        <v>18</v>
+      </c>
+      <c r="K37" s="2">
         <v>44503</v>
       </c>
       <c r="L37">
         <v>200</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:12">
       <c r="A38" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B38" t="s">
-        <v>13</v>
-      </c>
-      <c r="C38" s="2">
+        <v>14</v>
+      </c>
+      <c r="C38" s="1">
         <v>3</v>
       </c>
       <c r="D38" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E38" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F38">
         <v>54</v>
@@ -1901,33 +2484,33 @@
         <v>500</v>
       </c>
       <c r="I38" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J38" t="s">
-        <v>17</v>
-      </c>
-      <c r="K38" s="1">
+        <v>18</v>
+      </c>
+      <c r="K38" s="2">
         <v>44708</v>
       </c>
       <c r="L38">
         <v>232</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:12">
       <c r="A39" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B39" t="s">
-        <v>13</v>
-      </c>
-      <c r="C39" s="2">
+        <v>14</v>
+      </c>
+      <c r="C39" s="1">
         <v>3</v>
       </c>
       <c r="D39" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E39" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F39">
         <v>59</v>
@@ -1939,33 +2522,33 @@
         <v>500</v>
       </c>
       <c r="I39" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J39" t="s">
-        <v>17</v>
-      </c>
-      <c r="K39" s="1">
+        <v>18</v>
+      </c>
+      <c r="K39" s="2">
         <v>44708</v>
       </c>
       <c r="L39">
         <v>270</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:12">
       <c r="A40" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B40" t="s">
-        <v>13</v>
-      </c>
-      <c r="C40" s="2">
+        <v>14</v>
+      </c>
+      <c r="C40" s="1">
         <v>3</v>
       </c>
       <c r="D40" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E40" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F40">
         <v>70</v>
@@ -1977,33 +2560,33 @@
         <v>200</v>
       </c>
       <c r="I40" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J40" t="s">
-        <v>17</v>
-      </c>
-      <c r="K40" s="1">
+        <v>18</v>
+      </c>
+      <c r="K40" s="2">
         <v>44708</v>
       </c>
       <c r="L40">
         <v>115</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:12">
       <c r="A41" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B41" t="s">
-        <v>13</v>
-      </c>
-      <c r="C41" s="2">
+        <v>14</v>
+      </c>
+      <c r="C41" s="1">
         <v>3</v>
       </c>
       <c r="D41" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E41" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F41">
         <v>85</v>
@@ -2015,33 +2598,33 @@
         <v>200</v>
       </c>
       <c r="I41" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J41" t="s">
-        <v>17</v>
-      </c>
-      <c r="K41" s="1">
+        <v>18</v>
+      </c>
+      <c r="K41" s="2">
         <v>44708</v>
       </c>
       <c r="L41">
         <v>130</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:12">
       <c r="A42" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B42" t="s">
-        <v>13</v>
-      </c>
-      <c r="C42" s="2">
+        <v>14</v>
+      </c>
+      <c r="C42" s="1">
         <v>3</v>
       </c>
       <c r="D42" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E42" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F42">
         <v>99</v>
@@ -2053,33 +2636,33 @@
         <v>200</v>
       </c>
       <c r="I42" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J42" t="s">
-        <v>17</v>
-      </c>
-      <c r="K42" s="1">
+        <v>18</v>
+      </c>
+      <c r="K42" s="2">
         <v>44708</v>
       </c>
       <c r="L42">
         <v>91</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:12">
       <c r="A43" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B43" t="s">
-        <v>13</v>
-      </c>
-      <c r="C43" s="2">
+        <v>14</v>
+      </c>
+      <c r="C43" s="1">
         <v>3</v>
       </c>
       <c r="D43" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E43" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F43">
         <v>129</v>
@@ -2091,26 +2674,26 @@
         <v>200</v>
       </c>
       <c r="I43" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J43" t="s">
-        <v>17</v>
-      </c>
-      <c r="K43" s="1">
+        <v>18</v>
+      </c>
+      <c r="K43" s="2">
         <v>44708</v>
       </c>
       <c r="L43">
         <v>200</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:12">
       <c r="A44" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B44" t="s">
-        <v>13</v>
-      </c>
-      <c r="C44" s="2">
+        <v>14</v>
+      </c>
+      <c r="C44" s="1">
         <v>3</v>
       </c>
       <c r="F44">
@@ -2123,12 +2706,12 @@
         <v>5</v>
       </c>
       <c r="I44" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J44" t="s">
-        <v>17</v>
-      </c>
-      <c r="K44" s="1">
+        <v>18</v>
+      </c>
+      <c r="K44" s="2">
         <v>44734</v>
       </c>
       <c r="L44">
@@ -2137,5 +2720,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>